--- a/LoanOfficer-A/2023/18 Rambhabati- pishak.xlsx
+++ b/LoanOfficer-A/2023/18 Rambhabati- pishak.xlsx
@@ -327,7 +327,7 @@
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns="" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns="" val="0"/>
             </a:ext>
           </a:extLst>
         </a:blip>
@@ -605,7 +605,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -812,7 +812,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -821,7 +821,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>3200</v>
+        <v>3550</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>2800</v>
+        <v>2450</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1150,9 +1150,15 @@
       <c r="A12" s="1">
         <v>10</v>
       </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="1"/>
+      <c r="B12" s="3">
+        <v>45378</v>
+      </c>
+      <c r="C12" s="4">
+        <v>350</v>
+      </c>
+      <c r="D12" s="1">
+        <v>1</v>
+      </c>
       <c r="E12" s="1">
         <v>40</v>
       </c>

--- a/LoanOfficer-A/2023/18 Rambhabati- pishak.xlsx
+++ b/LoanOfficer-A/2023/18 Rambhabati- pishak.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="6" rupBuild="4505"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9302"/>
   <workbookPr filterPrivacy="1"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="3000" windowWidth="20640" windowHeight="11760" activeTab="1"/>
@@ -13,9 +13,9 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'MD10000.20-OCT'!$A$3:$N$32</definedName>
   </definedNames>
-  <calcPr calcId="124519" iterateDelta="1E-4"/>
-  <extLst xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+  <calcPr calcId="145621" iterateDelta="1E-4"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -106,12 +106,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yyyy;@"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -327,7 +327,7 @@
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns="" val="0"/>
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
             </a:ext>
           </a:extLst>
         </a:blip>
@@ -612,9 +612,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:C28"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="12"/>
     <col min="2" max="2" width="16.5703125" style="12" customWidth="1"/>
@@ -622,14 +622,14 @@
     <col min="4" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B2" s="21"/>
       <c r="C2" s="21"/>
     </row>
-    <row r="5" spans="2:3">
+    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B5" s="13"/>
     </row>
-    <row r="7" spans="2:3" ht="16.5">
+    <row r="7" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B7" s="14" t="s">
         <v>5</v>
       </c>
@@ -637,7 +637,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="2:3" ht="16.5">
+    <row r="8" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B8" s="14" t="s">
         <v>6</v>
       </c>
@@ -645,7 +645,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="2:3" ht="16.5">
+    <row r="9" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B9" s="14" t="s">
         <v>7</v>
       </c>
@@ -653,7 +653,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="2:3" ht="16.5">
+    <row r="10" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B10" s="14" t="s">
         <v>8</v>
       </c>
@@ -661,7 +661,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="2:3" ht="16.5">
+    <row r="11" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B11" s="14" t="s">
         <v>9</v>
       </c>
@@ -669,7 +669,7 @@
         <v>9863328343</v>
       </c>
     </row>
-    <row r="12" spans="2:3" ht="16.5">
+    <row r="12" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B12" s="14" t="s">
         <v>10</v>
       </c>
@@ -677,7 +677,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="2:3" ht="16.5">
+    <row r="13" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B13" s="14" t="s">
         <v>11</v>
       </c>
@@ -685,7 +685,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="14" spans="2:3" ht="16.5">
+    <row r="14" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B14" s="14" t="s">
         <v>12</v>
       </c>
@@ -693,47 +693,47 @@
         <v>120</v>
       </c>
     </row>
-    <row r="15" spans="2:3" ht="16.5">
+    <row r="15" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B15" s="14"/>
       <c r="C15" s="14"/>
     </row>
-    <row r="16" spans="2:3" ht="16.5">
+    <row r="16" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B16" s="16" t="s">
         <v>13</v>
       </c>
       <c r="C16" s="14"/>
     </row>
-    <row r="17" spans="2:3" ht="16.5">
+    <row r="17" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B17" s="22" t="s">
         <v>14</v>
       </c>
       <c r="C17" s="22"/>
     </row>
-    <row r="19" spans="2:3" ht="16.5">
+    <row r="19" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B19" s="17"/>
       <c r="C19" s="17"/>
     </row>
-    <row r="21" spans="2:3" ht="16.5">
+    <row r="21" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B21" s="22" t="s">
         <v>15</v>
       </c>
       <c r="C21" s="22"/>
     </row>
-    <row r="22" spans="2:3" ht="16.5">
+    <row r="22" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B22" s="14"/>
       <c r="C22" s="14"/>
     </row>
-    <row r="23" spans="2:3" ht="16.5">
+    <row r="23" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B23" s="14" t="s">
         <v>16</v>
       </c>
       <c r="C23" s="15"/>
     </row>
-    <row r="24" spans="2:3" ht="16.5">
+    <row r="24" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B24" s="14"/>
       <c r="C24" s="14"/>
     </row>
-    <row r="25" spans="2:3" ht="16.5">
+    <row r="25" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B25" s="14" t="s">
         <v>17</v>
       </c>
@@ -741,17 +741,17 @@
         <v>45212</v>
       </c>
     </row>
-    <row r="26" spans="2:3" ht="16.5">
+    <row r="26" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B26" s="14"/>
       <c r="C26" s="14"/>
     </row>
-    <row r="27" spans="2:3" ht="16.5">
+    <row r="27" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B27" s="14" t="s">
         <v>18</v>
       </c>
       <c r="C27" s="15"/>
     </row>
-    <row r="28" spans="2:3" ht="16.5">
+    <row r="28" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B28" s="14"/>
       <c r="C28" s="14"/>
     </row>
@@ -767,9 +767,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:P32"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="2" customWidth="1"/>
     <col min="2" max="2" width="19.140625" style="2" customWidth="1"/>
@@ -789,7 +789,7 @@
     <col min="17" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="5"/>
       <c r="B1" s="5" t="s">
         <v>0</v>
@@ -812,7 +812,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -821,11 +821,11 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>3550</v>
+        <v>4950</v>
       </c>
       <c r="P1" s="6"/>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="5"/>
       <c r="B2" s="5" t="s">
         <v>1</v>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,11 +854,11 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>2450</v>
+        <v>1050</v>
       </c>
       <c r="P2" s="6"/>
     </row>
-    <row r="3" spans="1:16" ht="16.5" customHeight="1">
+    <row r="3" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -890,7 +890,7 @@
       <c r="O3" s="4"/>
       <c r="P3" s="1"/>
     </row>
-    <row r="4" spans="1:16" ht="16.5" customHeight="1">
+    <row r="4" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -922,7 +922,7 @@
       <c r="O4" s="4"/>
       <c r="P4" s="1"/>
     </row>
-    <row r="5" spans="1:16" ht="16.5" customHeight="1">
+    <row r="5" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -954,7 +954,7 @@
       <c r="O5" s="4"/>
       <c r="P5" s="1"/>
     </row>
-    <row r="6" spans="1:16" ht="16.5" customHeight="1">
+    <row r="6" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -986,7 +986,7 @@
       <c r="O6" s="4"/>
       <c r="P6" s="1"/>
     </row>
-    <row r="7" spans="1:16" ht="16.5" customHeight="1">
+    <row r="7" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -1018,7 +1018,7 @@
       <c r="O7" s="4"/>
       <c r="P7" s="1"/>
     </row>
-    <row r="8" spans="1:16" ht="16.5" customHeight="1">
+    <row r="8" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -1050,7 +1050,7 @@
       <c r="O8" s="4"/>
       <c r="P8" s="1"/>
     </row>
-    <row r="9" spans="1:16" ht="16.5" customHeight="1">
+    <row r="9" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -1082,7 +1082,7 @@
       <c r="O9" s="4"/>
       <c r="P9" s="1"/>
     </row>
-    <row r="10" spans="1:16" ht="16.5" customHeight="1">
+    <row r="10" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -1114,7 +1114,7 @@
       <c r="O10" s="4"/>
       <c r="P10" s="1"/>
     </row>
-    <row r="11" spans="1:16" ht="16.5" customHeight="1">
+    <row r="11" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -1146,7 +1146,7 @@
       <c r="O11" s="4"/>
       <c r="P11" s="1"/>
     </row>
-    <row r="12" spans="1:16" ht="16.5" customHeight="1">
+    <row r="12" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -1178,13 +1178,19 @@
       <c r="O12" s="4"/>
       <c r="P12" s="1"/>
     </row>
-    <row r="13" spans="1:16" ht="16.5" customHeight="1">
+    <row r="13" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>11</v>
       </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="1"/>
+      <c r="B13" s="3">
+        <v>45385</v>
+      </c>
+      <c r="C13" s="4">
+        <v>350</v>
+      </c>
+      <c r="D13" s="1">
+        <v>1</v>
+      </c>
       <c r="E13" s="1">
         <v>41</v>
       </c>
@@ -1204,13 +1210,19 @@
       <c r="O13" s="4"/>
       <c r="P13" s="1"/>
     </row>
-    <row r="14" spans="1:16" ht="16.5" customHeight="1">
+    <row r="14" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>12</v>
       </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="1"/>
+      <c r="B14" s="3">
+        <v>45393</v>
+      </c>
+      <c r="C14" s="4">
+        <v>350</v>
+      </c>
+      <c r="D14" s="1">
+        <v>1</v>
+      </c>
       <c r="E14" s="1">
         <v>42</v>
       </c>
@@ -1230,13 +1242,19 @@
       <c r="O14" s="4"/>
       <c r="P14" s="1"/>
     </row>
-    <row r="15" spans="1:16" ht="16.5" customHeight="1">
+    <row r="15" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>13</v>
       </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="1"/>
+      <c r="B15" s="3">
+        <v>45406</v>
+      </c>
+      <c r="C15" s="4">
+        <v>350</v>
+      </c>
+      <c r="D15" s="1">
+        <v>1</v>
+      </c>
       <c r="E15" s="1">
         <v>43</v>
       </c>
@@ -1256,13 +1274,19 @@
       <c r="O15" s="4"/>
       <c r="P15" s="1"/>
     </row>
-    <row r="16" spans="1:16" ht="16.5" customHeight="1">
+    <row r="16" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>14</v>
       </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="1"/>
+      <c r="B16" s="3">
+        <v>45413</v>
+      </c>
+      <c r="C16" s="4">
+        <v>350</v>
+      </c>
+      <c r="D16" s="1">
+        <v>1</v>
+      </c>
       <c r="E16" s="1">
         <v>44</v>
       </c>
@@ -1282,7 +1306,7 @@
       <c r="O16" s="4"/>
       <c r="P16" s="1"/>
     </row>
-    <row r="17" spans="1:16" ht="16.5" customHeight="1">
+    <row r="17" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -1308,7 +1332,7 @@
       <c r="O17" s="4"/>
       <c r="P17" s="1"/>
     </row>
-    <row r="18" spans="1:16" ht="16.5" customHeight="1">
+    <row r="18" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -1334,7 +1358,7 @@
       <c r="O18" s="4"/>
       <c r="P18" s="1"/>
     </row>
-    <row r="19" spans="1:16" ht="16.5" customHeight="1">
+    <row r="19" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -1360,7 +1384,7 @@
       <c r="O19" s="4"/>
       <c r="P19" s="1"/>
     </row>
-    <row r="20" spans="1:16" ht="16.5" customHeight="1">
+    <row r="20" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -1386,7 +1410,7 @@
       <c r="O20" s="4"/>
       <c r="P20" s="1"/>
     </row>
-    <row r="21" spans="1:16" ht="16.5" customHeight="1">
+    <row r="21" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -1412,7 +1436,7 @@
       <c r="O21" s="4"/>
       <c r="P21" s="1"/>
     </row>
-    <row r="22" spans="1:16" ht="16.5" customHeight="1">
+    <row r="22" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -1438,7 +1462,7 @@
       <c r="O22" s="4"/>
       <c r="P22" s="1"/>
     </row>
-    <row r="23" spans="1:16" ht="16.5" customHeight="1">
+    <row r="23" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -1464,7 +1488,7 @@
       <c r="O23" s="4"/>
       <c r="P23" s="1"/>
     </row>
-    <row r="24" spans="1:16" ht="16.5" customHeight="1">
+    <row r="24" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -1490,7 +1514,7 @@
       <c r="O24" s="4"/>
       <c r="P24" s="1"/>
     </row>
-    <row r="25" spans="1:16" ht="16.5" customHeight="1">
+    <row r="25" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>23</v>
       </c>
@@ -1516,7 +1540,7 @@
       <c r="O25" s="4"/>
       <c r="P25" s="1"/>
     </row>
-    <row r="26" spans="1:16" ht="16.5" customHeight="1">
+    <row r="26" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>24</v>
       </c>
@@ -1542,7 +1566,7 @@
       <c r="O26" s="4"/>
       <c r="P26" s="1"/>
     </row>
-    <row r="27" spans="1:16" ht="16.5" customHeight="1">
+    <row r="27" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>25</v>
       </c>
@@ -1568,7 +1592,7 @@
       <c r="O27" s="4"/>
       <c r="P27" s="1"/>
     </row>
-    <row r="28" spans="1:16" ht="16.5" customHeight="1">
+    <row r="28" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>26</v>
       </c>
@@ -1594,7 +1618,7 @@
       <c r="O28" s="4"/>
       <c r="P28" s="1"/>
     </row>
-    <row r="29" spans="1:16" ht="16.5" customHeight="1">
+    <row r="29" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>27</v>
       </c>
@@ -1620,7 +1644,7 @@
       <c r="O29" s="4"/>
       <c r="P29" s="1"/>
     </row>
-    <row r="30" spans="1:16" ht="16.5" customHeight="1">
+    <row r="30" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>28</v>
       </c>
@@ -1646,7 +1670,7 @@
       <c r="O30" s="4"/>
       <c r="P30" s="1"/>
     </row>
-    <row r="31" spans="1:16" ht="16.5" customHeight="1">
+    <row r="31" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>29</v>
       </c>
@@ -1672,7 +1696,7 @@
       <c r="O31" s="4"/>
       <c r="P31" s="1"/>
     </row>
-    <row r="32" spans="1:16" ht="16.5" customHeight="1">
+    <row r="32" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>30</v>
       </c>

--- a/LoanOfficer-A/2023/18 Rambhabati- pishak.xlsx
+++ b/LoanOfficer-A/2023/18 Rambhabati- pishak.xlsx
@@ -812,7 +812,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -821,7 +821,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>4950</v>
+        <v>5650</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>1050</v>
+        <v>350</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1310,9 +1310,15 @@
       <c r="A17" s="1">
         <v>15</v>
       </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="1"/>
+      <c r="B17" s="3">
+        <v>45420</v>
+      </c>
+      <c r="C17" s="4">
+        <v>350</v>
+      </c>
+      <c r="D17" s="1">
+        <v>1</v>
+      </c>
       <c r="E17" s="1">
         <v>45</v>
       </c>
@@ -1336,9 +1342,15 @@
       <c r="A18" s="1">
         <v>16</v>
       </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="1"/>
+      <c r="B18" s="3">
+        <v>45423</v>
+      </c>
+      <c r="C18" s="4">
+        <v>350</v>
+      </c>
+      <c r="D18" s="1">
+        <v>1</v>
+      </c>
       <c r="E18" s="1">
         <v>46</v>
       </c>
